--- a/server/excel/release/recharge-benefit.xlsx
+++ b/server/excel/release/recharge-benefit.xlsx
@@ -143,7 +143,7 @@
     <t xml:space="preserve">icon2</t>
   </si>
   <si>
-    <t xml:space="preserve">Gói quà chiêu mộ anh hùng</t>
+    <t xml:space="preserve">Gói quà chiêu mộ tướng</t>
   </si>
   <si>
     <t xml:space="preserve">3:100025:3#3:100001:1000#0:0:100000</t>
@@ -1061,7 +1061,7 @@
     <t xml:space="preserve">0:4:5000000</t>
   </si>
   <si>
-    <t xml:space="preserve">Anh hùng kinh nghiệm</t>
+    <t xml:space="preserve">Tướng kinh nghiệm</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:500</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">500元宝，1000进阶石，500w金币，500w经验</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 6 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 6 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">9 Tinh gói quà</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">680元宝，紫色符文，1000w金币，1000w经验</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 9 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 9 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">10 Tinh gói quà</t>
@@ -1409,7 +1409,7 @@
     <t xml:space="preserve">1280元宝，2随机篆印礼包，紫色符文，5000鎏金粉</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 10 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 10 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">5 Tinh gói quà</t>
@@ -1421,7 +1421,7 @@
     <t xml:space="preserve">300元宝，1000进阶石，300w金币，300w经验</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 5 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 5 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">11 Tinh gói quà</t>
@@ -1433,7 +1433,7 @@
     <t xml:space="preserve">3280元宝，金色符文，1w鎏金粉，2000w金币</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 11 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 11 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:3280#5:4:2#3:100004:20000#0:0:30000000</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">元宝*6480，灌魔之瓶*30，金币*5000w，经验*5000w</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 12 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 12 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:6480#3:500015:50#0:0:50000000#0:4:50000000</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">元宝*6480，红色玺印*1，1w鎏金粉，龙魂*4</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 13 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 13 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:6480#5:5:1#3:100004:20000#5:20001:6</t>
@@ -1493,7 +1493,7 @@
     <t xml:space="preserve">元宝*6480,藏品币*60，金币*5000w，经验*5000w</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 14 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 14 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">14 Tinh đột phá gói quà</t>
@@ -1505,7 +1505,7 @@
     <t xml:space="preserve">元宝*6480,破境丹*1700，金币*5000w，经验*5000w</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài thu được 14 Tinh anh hùng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà có thể đột phá anh hùng cảnh giới</t>
+    <t xml:space="preserve">Chúc mừng ngài thu được 14 Tinh tướng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà có thể đột phá tướng cảnh giới</t>
   </si>
   <si>
     <t xml:space="preserve">Linh Lung Tháp gói quà 1</t>
@@ -1829,7 +1829,7 @@
     <t xml:space="preserve">Chiến lực gói quà 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài chiến lực đạt tới 10 Vạn, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài chiến lực đạt tới 100K, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lực gói quà 2</t>
@@ -1841,7 +1841,7 @@
     <t xml:space="preserve">1280元宝，100五星随机，1000w金币，1000w经验</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài chiến lực đạt tới 20 Vạn, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài chiến lực đạt tới 200K, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lực gói quà 3</t>
@@ -1853,13 +1853,13 @@
     <t xml:space="preserve">1280元宝，神魔随机，1000w金币，1000w经验</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài chiến lực đạt tới 40 Vạn, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài chiến lực đạt tới 400K, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">Chiến lực gói quà 4</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài chiến lực đạt tới 50 Vạn, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài chiến lực đạt tới 500K, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">Lục soát thần kỷ gói quà 1</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">Chúc mừng ngài thú hồn tẩy luyện 50 Lần, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
-    <t xml:space="preserve">Đẳng cấp gói quà 1</t>
+    <t xml:space="preserve">Cấp gói quà 1</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:3280#3:500015:10#3:100025:5#0:0:20000000</t>
@@ -2084,10 +2084,10 @@
     <t xml:space="preserve">888</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài đẳng cấp đạt tới 90 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp gói quà 2</t>
+    <t xml:space="preserve">Chúc mừng ngài cấp đạt tới 90 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp gói quà 2</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:6480#3:500015:20#3:100025:10#0:0:30000000</t>
@@ -2102,10 +2102,10 @@
     <t xml:space="preserve">104</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài đẳng cấp đạt tới 100 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp gói quà 3</t>
+    <t xml:space="preserve">Chúc mừng ngài cấp đạt tới 100 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp gói quà 3</t>
   </si>
   <si>
     <t xml:space="preserve">105</t>
@@ -2114,10 +2114,10 @@
     <t xml:space="preserve">109</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài đẳng cấp đạt tới 105 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp gói quà 4</t>
+    <t xml:space="preserve">Chúc mừng ngài cấp đạt tới 105 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp gói quà 4</t>
   </si>
   <si>
     <t xml:space="preserve">110</t>
@@ -2126,10 +2126,10 @@
     <t xml:space="preserve">114</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài đẳng cấp đạt tới 110 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp gói quà 5</t>
+    <t xml:space="preserve">Chúc mừng ngài cấp đạt tới 110 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp gói quà 5</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:6480#3:400029:1#3:100059:350#0:0:30000000</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">119</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài đẳng cấp đạt tới 115 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp gói quà 6</t>
+    <t xml:space="preserve">Chúc mừng ngài cấp đạt tới 115 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp gói quà 6</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:6480#3:500013:1#3:100059:400#0:0:30000000</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">124</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài đẳng cấp đạt tới 120 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp gói quà 7</t>
+    <t xml:space="preserve">Chúc mừng ngài cấp đạt tới 120 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp gói quà 7</t>
   </si>
   <si>
     <t xml:space="preserve">元宝*6480，专属仙器自选，仙玉*3w，金币*2000w</t>
@@ -2177,28 +2177,28 @@
     <t xml:space="preserve">129</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài đẳng cấp đạt tới 125 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Đẳng cấp gói quà 8</t>
+    <t xml:space="preserve">Chúc mừng ngài cấp đạt tới 125 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cấp gói quà 8</t>
   </si>
   <si>
     <t xml:space="preserve">130</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài đẳng cấp đạt tới 130 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài cấp đạt tới 130 Cấp, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">220001</t>
   </si>
   <si>
-    <t xml:space="preserve">Treo máy ban thưởng gói quà</t>
+    <t xml:space="preserve">Treo máy thưởng gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">1007</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng ngài nhận lấy treo máy ban thưởng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng ngài nhận treo máy thưởng, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">230001</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">418</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng thăng tinh anh hùng đạt tới thập tinh, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng thăng tinh tướng đạt tới thập tinh, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">230002</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">231001</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng thăng tinh anh hùng đạt tới mười một tinh, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng thăng tinh tướng đạt tới mười một tinh, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">46501</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">0:1:1980#3:100256:10#0:0:15000000#0:4:15000000</t>
   </si>
   <si>
-    <t xml:space="preserve">Chúc mừng thu hoạch được tinh anh trang bị, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
+    <t xml:space="preserve">Chúc mừng nhận được tinh anh trang bị, chúng ta vì ngài chuẩn bị siêu giá trị gói quà</t>
   </si>
   <si>
     <t xml:space="preserve">0:1:3280#3:100257:10#0:0:20000000#0:4:20000000</t>

--- a/server/excel/release/recharge-benefit.xlsx
+++ b/server/excel/release/recharge-benefit.xlsx
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">0:1:1000</t>
   </si>
   <si>
-    <t xml:space="preserve">Nguyên bảo</t>
+    <t xml:space="preserve">Kim cương</t>
   </si>
   <si>
     <t xml:space="preserve">4:606002:50</t>
